--- a/benchmarks/osworld/results/agent_computer_sonnet5/881deb30-9549-4583-a841-8270c65f2a17/run_1/supported_rate.xlsx
+++ b/benchmarks/osworld/results/agent_computer_sonnet5/881deb30-9549-4583-a841-8270c65f2a17/run_1/supported_rate.xlsx
@@ -194,28 +194,28 @@
         <v>2015</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.4545454545</v>
+        <v>0.454545</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>0.44</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.7142857143</v>
+        <v>0.714286</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.4576271186</v>
+        <v>0.457627</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.3090909091</v>
+        <v>0.309091</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.3116883117</v>
+        <v>0.311688</v>
       </c>
       <c r="H2" s="0" t="n">
         <v>0.4375</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.4032258065</v>
+        <v>0.403226</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -223,28 +223,28 @@
         <v>2016</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.4915254237</v>
+        <v>0.491525</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.3846153846</v>
+        <v>0.384615</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0.6</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.3793103448</v>
+        <v>0.37931</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>0.2</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.3783783784</v>
+        <v>0.378378</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.7083333333</v>
+        <v>0.708333</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.4857142857</v>
+        <v>0.485714</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -252,25 +252,25 @@
         <v>2017</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.4318181818</v>
+        <v>0.431818</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.3103448276</v>
+        <v>0.310345</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.6666666667</v>
+        <v>0.666667</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.3421052632</v>
+        <v>0.342105</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.2894736842</v>
+        <v>0.289474</v>
       </c>
       <c r="G4" s="0" t="n">
         <v>0.37</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.5714285714</v>
+        <v>0.571429</v>
       </c>
       <c r="I4" s="0" t="n">
         <v>0.375</v>
@@ -281,28 +281,28 @@
         <v>2018</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.4181818182</v>
+        <v>0.418182</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.2926829268</v>
+        <v>0.292683</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.6666666667</v>
+        <v>0.666667</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.4246575342</v>
+        <v>0.424658</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.3666666667</v>
+        <v>0.366667</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.3333333333</v>
+        <v>0.333333</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.5925925926</v>
+        <v>0.592593</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.4032258065</v>
+        <v>0.403226</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -310,28 +310,28 @@
         <v>2019</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.4090909091</v>
+        <v>0.409091</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.2926829268</v>
+        <v>0.292683</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.4444444444</v>
+        <v>0.444444</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.3913043478</v>
+        <v>0.391304</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>0.36</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.3768115942</v>
+        <v>0.376812</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.5789473684</v>
+        <v>0.578947</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.4918032787</v>
+        <v>0.491803</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -339,25 +339,25 @@
         <v>2020</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.3506493506</v>
+        <v>0.350649</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.303030303</v>
+        <v>0.30303</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.347826087</v>
+        <v>0.347826</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.3943661972</v>
+        <v>0.394366</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.3181818182</v>
+        <v>0.318182</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.3220338983</v>
+        <v>0.322034</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.487804878</v>
+        <v>0.487805</v>
       </c>
       <c r="I7" s="0" t="n">
         <v>0.5</v>
@@ -368,28 +368,28 @@
         <v>2021</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.4473684211</v>
+        <v>0.447368</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>0.4</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.2068965517</v>
+        <v>0.206897</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.4810126582</v>
+        <v>0.481013</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.347826087</v>
+        <v>0.347826</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.2857142857</v>
+        <v>0.285714</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.4651162791</v>
+        <v>0.465116</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.5119047619</v>
+        <v>0.511905</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -397,28 +397,28 @@
         <v>2022</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.3048780488</v>
+        <v>0.304878</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.1538461538</v>
+        <v>0.153846</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>0.28</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.4086021505</v>
+        <v>0.408602</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.3333333333</v>
+        <v>0.333333</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.2769230769</v>
+        <v>0.276923</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.2727272727</v>
+        <v>0.272727</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.3536585366</v>
+        <v>0.353659</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -426,28 +426,28 @@
         <v>2023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.3522727273</v>
+        <v>0.352273</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.2545454545</v>
+        <v>0.254545</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.4666666667</v>
+        <v>0.466667</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.3176470588</v>
+        <v>0.317647</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.2272727273</v>
+        <v>0.227273</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.4084507042</v>
+        <v>0.408451</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.4655172414</v>
+        <v>0.465517</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.3448275862</v>
+        <v>0.344828</v>
       </c>
     </row>
   </sheetData>
